--- a/PartsList.xlsx
+++ b/PartsList.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\matja\Documents\Projects\PCBs\Keyboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89903664-EBFD-4C7E-9804-02D1DAC955E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD9F0841-BB31-46B4-A99D-25E84776080D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="24240" windowHeight="13020" activeTab="3" xr2:uid="{FE2F31EC-1493-4486-83E7-300EEFA8040E}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="24240" windowHeight="13020" activeTab="2" xr2:uid="{FE2F31EC-1493-4486-83E7-300EEFA8040E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="247">
   <si>
     <t>Name</t>
   </si>
@@ -443,9 +443,6 @@
     <t>M2.5 Standoff</t>
   </si>
   <si>
-    <t>https://www.mouser.co.za/ProductDetail/Wurth-Elektronik/970050144?qs=%252BEew9%252B0nqrC1EgXDL0bofw%3D%3D</t>
-  </si>
-  <si>
     <t>Gaskets</t>
   </si>
   <si>
@@ -738,6 +735,51 @@
   </si>
   <si>
     <t>No Stock of 1</t>
+  </si>
+  <si>
+    <t>https://www.digikey.co.za/en/products/detail/würth-elektronik/970080144/9488538</t>
+  </si>
+  <si>
+    <t>M2.5x5mm Standoff</t>
+  </si>
+  <si>
+    <t>https://za.rs-online.com/web/p/standoffs/2052903</t>
+  </si>
+  <si>
+    <t>Final</t>
+  </si>
+  <si>
+    <t>M2.5x8mm Standoff</t>
+  </si>
+  <si>
+    <t>https://za.rs-online.com/web/p/standoffs/2052905?gb=s</t>
+  </si>
+  <si>
+    <t>Set</t>
+  </si>
+  <si>
+    <t>Set - 150</t>
+  </si>
+  <si>
+    <t>Gasket</t>
+  </si>
+  <si>
+    <t>M2.5 Screw</t>
+  </si>
+  <si>
+    <t>M2.5 Insert</t>
+  </si>
+  <si>
+    <t>Foam Layer</t>
+  </si>
+  <si>
+    <t>https://za.rs-online.com/web/p/foam-inserts/1368892?gb=s</t>
+  </si>
+  <si>
+    <t>https://za.rs-online.com/web/p/machine-screws/9141630?gb=s</t>
+  </si>
+  <si>
+    <t>https://www.digikey.co.za/en/products/detail/harvatek-corporation/T36K3BGR-05D000121U1930/13588739?srsltid=AfmBOorHMRRNAUi7aH5xRNijnPW6IsY_VAwZrTEPsSnwkcwYHddkkWbw</t>
   </si>
 </sst>
 </file>
@@ -747,7 +789,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;R&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -769,6 +811,12 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -792,7 +840,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <extLst>
@@ -807,6 +855,7 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3785,7 +3834,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59C7F33A-CEE5-46B8-B073-2F922778444F}">
-  <dimension ref="A1:T67"/>
+  <dimension ref="A1:T68"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.7109375" customWidth="1"/>
@@ -3864,7 +3913,7 @@
       </c>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="9" t="s">
         <v>7</v>
       </c>
       <c r="B2" s="5" t="s">
@@ -3924,11 +3973,11 @@
         <v>77</v>
       </c>
       <c r="T2" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A3" s="8"/>
+      <c r="A3" s="9"/>
       <c r="B3" s="5" t="s">
         <v>58</v>
       </c>
@@ -3984,7 +4033,7 @@
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A4" s="8"/>
+      <c r="A4" s="9"/>
       <c r="B4" s="5" t="s">
         <v>59</v>
       </c>
@@ -4040,7 +4089,7 @@
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A5" s="8"/>
+      <c r="A5" s="9"/>
       <c r="B5" s="5" t="s">
         <v>56</v>
       </c>
@@ -4096,7 +4145,7 @@
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A6" s="8"/>
+      <c r="A6" s="9"/>
       <c r="B6" s="5" t="s">
         <v>57</v>
       </c>
@@ -4152,7 +4201,7 @@
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A7" s="8"/>
+      <c r="A7" s="9"/>
       <c r="B7" s="5" t="s">
         <v>60</v>
       </c>
@@ -4220,7 +4269,7 @@
       <c r="L8" s="4"/>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A9" s="9" t="s">
+      <c r="A9" s="10" t="s">
         <v>11</v>
       </c>
       <c r="B9" s="5" t="s">
@@ -4281,7 +4330,7 @@
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A10" s="9"/>
+      <c r="A10" s="10"/>
       <c r="B10" s="5" t="s">
         <v>64</v>
       </c>
@@ -4340,7 +4389,7 @@
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A11" s="9"/>
+      <c r="A11" s="10"/>
       <c r="B11" s="5" t="s">
         <v>65</v>
       </c>
@@ -4395,11 +4444,11 @@
         <v>85</v>
       </c>
       <c r="T11" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A12" s="9"/>
+      <c r="A12" s="10"/>
       <c r="B12" s="5" t="s">
         <v>101</v>
       </c>
@@ -4458,7 +4507,7 @@
       </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A13" s="9"/>
+      <c r="A13" s="10"/>
       <c r="B13" s="5">
         <v>20</v>
       </c>
@@ -4514,7 +4563,7 @@
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A14" s="9"/>
+      <c r="A14" s="10"/>
       <c r="B14" s="5">
         <v>51</v>
       </c>
@@ -4563,14 +4612,14 @@
         <v>81</v>
       </c>
       <c r="Q14" s="6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="T14" s="1" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A15" s="9"/>
+      <c r="A15" s="10"/>
       <c r="B15" s="5" t="s">
         <v>66</v>
       </c>
@@ -4626,7 +4675,7 @@
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A16" s="9"/>
+      <c r="A16" s="10"/>
       <c r="B16" s="5" t="s">
         <v>103</v>
       </c>
@@ -4926,7 +4975,7 @@
       </c>
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A22" s="9" t="s">
+      <c r="A22" s="10" t="s">
         <v>68</v>
       </c>
       <c r="B22" s="5" t="s">
@@ -4981,7 +5030,7 @@
       </c>
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A23" s="9"/>
+      <c r="A23" s="10"/>
       <c r="B23" s="5" t="s">
         <v>110</v>
       </c>
@@ -5028,7 +5077,7 @@
       </c>
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A24" s="9"/>
+      <c r="A24" s="10"/>
       <c r="B24" s="5" t="s">
         <v>70</v>
       </c>
@@ -5119,7 +5168,7 @@
         <v>148.63092</v>
       </c>
       <c r="L25" s="4">
-        <f t="shared" si="10"/>
+        <f>IF($M25, $H25*F25, 0)</f>
         <v>247.7182</v>
       </c>
       <c r="M25" s="1" t="b">
@@ -5181,7 +5230,7 @@
         <v>0</v>
       </c>
       <c r="T26" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.25">
@@ -5662,7 +5711,7 @@
         <v>119</v>
       </c>
       <c r="T35" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:20" x14ac:dyDescent="0.25">
@@ -5692,18 +5741,18 @@
         <v>133</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>134</v>
+        <v>232</v>
       </c>
       <c r="K37" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="38" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
+        <v>134</v>
+      </c>
+      <c r="B38" s="5" t="s">
         <v>135</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="39" spans="1:20" x14ac:dyDescent="0.25">
@@ -5713,26 +5762,26 @@
     </row>
     <row r="40" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
+        <v>137</v>
+      </c>
+      <c r="B40" s="5" t="s">
         <v>138</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="41" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="42" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="44" spans="1:20" x14ac:dyDescent="0.25">
@@ -5751,43 +5800,162 @@
         <v>900</v>
       </c>
     </row>
-    <row r="53" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C53" s="3"/>
-      <c r="D53" s="3"/>
-      <c r="E53" s="3"/>
-      <c r="I53" s="4"/>
-      <c r="J53" s="4"/>
-      <c r="K53" s="4"/>
-      <c r="L53" s="4"/>
-    </row>
-    <row r="54" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="48" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>233</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="H48" s="8">
+        <v>9.5809999999999995</v>
+      </c>
+      <c r="J48">
+        <v>15</v>
+      </c>
+      <c r="K48" s="4"/>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>236</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="H49" s="8">
+        <v>11.041</v>
+      </c>
+      <c r="J49">
+        <v>30</v>
+      </c>
+      <c r="K49" s="4">
+        <f t="shared" ref="K49:K54" si="21">H49*J49</f>
+        <v>331.23</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>241</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="H50" s="8">
+        <v>0.97699999999999998</v>
+      </c>
+      <c r="J50">
+        <v>100</v>
+      </c>
+      <c r="K50" s="4">
+        <f t="shared" si="21"/>
+        <v>97.7</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>242</v>
+      </c>
+      <c r="K51" s="4">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>142</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="H52" s="4">
+        <v>273.99</v>
+      </c>
+      <c r="I52" t="s">
+        <v>239</v>
+      </c>
+      <c r="J52">
+        <v>1</v>
+      </c>
+      <c r="K52" s="4">
+        <f t="shared" si="21"/>
+        <v>273.99</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>240</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="H53">
+        <v>157.58000000000001</v>
+      </c>
+      <c r="I53" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="J53">
+        <v>1</v>
+      </c>
+      <c r="K53" s="4">
+        <f t="shared" si="21"/>
+        <v>157.58000000000001</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>243</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>244</v>
+      </c>
       <c r="C54" s="3"/>
       <c r="D54" s="3"/>
       <c r="E54" s="3"/>
-      <c r="I54" s="4"/>
-      <c r="J54" s="4"/>
-      <c r="K54" s="4"/>
+      <c r="H54">
+        <v>76.98</v>
+      </c>
+      <c r="J54">
+        <v>2</v>
+      </c>
+      <c r="K54" s="4">
+        <f t="shared" si="21"/>
+        <v>153.96</v>
+      </c>
       <c r="L54" s="4"/>
     </row>
-    <row r="55" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>13</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>246</v>
+      </c>
       <c r="C55" s="3"/>
       <c r="D55" s="3"/>
       <c r="E55" s="3"/>
       <c r="I55" s="4"/>
       <c r="J55" s="4"/>
-      <c r="K55" s="4"/>
       <c r="L55" s="4"/>
     </row>
-    <row r="56" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C56" s="3"/>
       <c r="D56" s="3"/>
       <c r="E56" s="3"/>
       <c r="I56" s="4"/>
       <c r="J56" s="4"/>
-      <c r="K56" s="4"/>
+      <c r="K56" s="4">
+        <f>SUM(K48:K55)</f>
+        <v>1014.4600000000002</v>
+      </c>
       <c r="L56" s="4"/>
     </row>
-    <row r="57" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C57" s="3"/>
       <c r="D57" s="3"/>
       <c r="E57" s="3"/>
@@ -5796,7 +5964,7 @@
       <c r="K57" s="4"/>
       <c r="L57" s="4"/>
     </row>
-    <row r="58" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C58" s="3"/>
       <c r="D58" s="3"/>
       <c r="E58" s="3"/>
@@ -5805,7 +5973,7 @@
       <c r="K58" s="4"/>
       <c r="L58" s="4"/>
     </row>
-    <row r="59" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C59" s="3"/>
       <c r="D59" s="3"/>
       <c r="E59" s="3"/>
@@ -5814,7 +5982,7 @@
       <c r="K59" s="4"/>
       <c r="L59" s="4"/>
     </row>
-    <row r="60" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C60" s="3"/>
       <c r="D60" s="3"/>
       <c r="E60" s="3"/>
@@ -5823,7 +5991,7 @@
       <c r="K60" s="4"/>
       <c r="L60" s="4"/>
     </row>
-    <row r="61" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C61" s="3"/>
       <c r="D61" s="3"/>
       <c r="E61" s="3"/>
@@ -5832,7 +6000,7 @@
       <c r="K61" s="4"/>
       <c r="L61" s="4"/>
     </row>
-    <row r="62" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C62" s="3"/>
       <c r="D62" s="3"/>
       <c r="E62" s="3"/>
@@ -5841,7 +6009,7 @@
       <c r="K62" s="4"/>
       <c r="L62" s="4"/>
     </row>
-    <row r="63" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C63" s="3"/>
       <c r="D63" s="3"/>
       <c r="E63" s="3"/>
@@ -5850,7 +6018,7 @@
       <c r="K63" s="4"/>
       <c r="L63" s="4"/>
     </row>
-    <row r="64" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C64" s="3"/>
       <c r="D64" s="3"/>
       <c r="E64" s="3"/>
@@ -5878,10 +6046,19 @@
       <c r="L66" s="4"/>
     </row>
     <row r="67" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C67" s="3"/>
+      <c r="D67" s="3"/>
+      <c r="E67" s="3"/>
       <c r="I67" s="4"/>
       <c r="J67" s="4"/>
       <c r="K67" s="4"/>
       <c r="L67" s="4"/>
+    </row>
+    <row r="68" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="I68" s="4"/>
+      <c r="J68" s="4"/>
+      <c r="K68" s="4"/>
+      <c r="L68" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -5934,25 +6111,25 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B1" t="s">
         <v>145</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>146</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>147</v>
       </c>
-      <c r="D1" t="s">
-        <v>148</v>
-      </c>
       <c r="E1" t="s">
+        <v>217</v>
+      </c>
+      <c r="F1" t="s">
         <v>218</v>
       </c>
-      <c r="F1" t="s">
-        <v>219</v>
-      </c>
       <c r="H1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -5960,19 +6137,19 @@
         <v>59</v>
       </c>
       <c r="B2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C2" t="s">
         <v>149</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>150</v>
       </c>
-      <c r="D2" t="s">
-        <v>151</v>
-      </c>
       <c r="E2" s="1" t="b">
         <v>1</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H2" t="str">
         <f>IF(E2,F2,D2)</f>
@@ -5984,13 +6161,13 @@
         <v>58</v>
       </c>
       <c r="B3" t="s">
+        <v>151</v>
+      </c>
+      <c r="C3" t="s">
+        <v>149</v>
+      </c>
+      <c r="D3" t="s">
         <v>152</v>
-      </c>
-      <c r="C3" t="s">
-        <v>150</v>
-      </c>
-      <c r="D3" t="s">
-        <v>153</v>
       </c>
       <c r="E3" s="1" t="b">
         <v>0</v>
@@ -6005,19 +6182,19 @@
         <v>60</v>
       </c>
       <c r="B4" t="s">
+        <v>153</v>
+      </c>
+      <c r="C4" t="s">
+        <v>149</v>
+      </c>
+      <c r="D4" t="s">
         <v>154</v>
       </c>
-      <c r="C4" t="s">
-        <v>150</v>
-      </c>
-      <c r="D4" t="s">
-        <v>155</v>
-      </c>
       <c r="E4" s="1" t="b">
         <v>1</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H4" t="str">
         <f t="shared" si="0"/>
@@ -6029,19 +6206,19 @@
         <v>56</v>
       </c>
       <c r="B5" t="s">
+        <v>155</v>
+      </c>
+      <c r="C5" t="s">
         <v>156</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>157</v>
       </c>
-      <c r="D5" t="s">
-        <v>158</v>
-      </c>
       <c r="E5" s="1" t="b">
         <v>1</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H5" t="str">
         <f t="shared" si="0"/>
@@ -6053,19 +6230,19 @@
         <v>55</v>
       </c>
       <c r="B6" t="s">
+        <v>158</v>
+      </c>
+      <c r="C6" t="s">
         <v>159</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>160</v>
       </c>
-      <c r="D6" t="s">
-        <v>161</v>
-      </c>
       <c r="E6" s="1" t="b">
         <v>1</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H6" t="str">
         <f t="shared" si="0"/>
@@ -6077,19 +6254,19 @@
         <v>57</v>
       </c>
       <c r="B7" t="s">
+        <v>161</v>
+      </c>
+      <c r="C7" t="s">
         <v>162</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>163</v>
       </c>
-      <c r="D7" t="s">
-        <v>164</v>
-      </c>
       <c r="E7" s="1" t="b">
         <v>1</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H7" t="str">
         <f t="shared" si="0"/>
@@ -6101,19 +6278,19 @@
         <v>8</v>
       </c>
       <c r="B8" t="s">
+        <v>164</v>
+      </c>
+      <c r="C8" t="s">
         <v>165</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>166</v>
       </c>
-      <c r="D8" t="s">
-        <v>167</v>
-      </c>
       <c r="E8" s="1" t="b">
         <v>1</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H8" t="str">
         <f t="shared" si="0"/>
@@ -6122,16 +6299,16 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>167</v>
+      </c>
+      <c r="B9" t="s">
         <v>168</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>169</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
         <v>170</v>
-      </c>
-      <c r="D9" t="s">
-        <v>171</v>
       </c>
       <c r="E9" s="1" t="b">
         <v>0</v>
@@ -6143,16 +6320,16 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>171</v>
+      </c>
+      <c r="B10" t="s">
         <v>172</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
         <v>173</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>174</v>
-      </c>
-      <c r="D10" t="s">
-        <v>175</v>
       </c>
       <c r="E10" s="1" t="b">
         <v>0</v>
@@ -6167,19 +6344,19 @@
         <v>64</v>
       </c>
       <c r="B11" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="C11" t="s">
         <v>176</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
         <v>177</v>
       </c>
-      <c r="D11" t="s">
-        <v>178</v>
-      </c>
       <c r="E11" s="1" t="b">
         <v>1</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H11" t="str">
         <f t="shared" si="0"/>
@@ -6191,19 +6368,19 @@
         <v>65</v>
       </c>
       <c r="B12" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="C12" t="s">
+        <v>176</v>
+      </c>
+      <c r="D12" t="s">
         <v>179</v>
       </c>
-      <c r="C12" t="s">
-        <v>177</v>
-      </c>
-      <c r="D12" t="s">
-        <v>180</v>
-      </c>
       <c r="E12" s="1" t="b">
         <v>1</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H12" t="str">
         <f t="shared" si="0"/>
@@ -6215,13 +6392,13 @@
         <v>51</v>
       </c>
       <c r="B13" t="s">
+        <v>180</v>
+      </c>
+      <c r="C13" t="s">
+        <v>176</v>
+      </c>
+      <c r="D13" t="s">
         <v>181</v>
-      </c>
-      <c r="C13" t="s">
-        <v>177</v>
-      </c>
-      <c r="D13" t="s">
-        <v>182</v>
       </c>
       <c r="E13" s="1" t="b">
         <v>0</v>
@@ -6236,13 +6413,13 @@
         <v>66</v>
       </c>
       <c r="B14" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="C14" t="s">
+        <v>176</v>
+      </c>
+      <c r="D14" t="s">
         <v>183</v>
-      </c>
-      <c r="C14" t="s">
-        <v>177</v>
-      </c>
-      <c r="D14" t="s">
-        <v>184</v>
       </c>
       <c r="E14" s="1" t="b">
         <v>0</v>
@@ -6257,13 +6434,13 @@
         <v>20</v>
       </c>
       <c r="B15" t="s">
+        <v>184</v>
+      </c>
+      <c r="C15" t="s">
+        <v>176</v>
+      </c>
+      <c r="D15" t="s">
         <v>185</v>
-      </c>
-      <c r="C15" t="s">
-        <v>177</v>
-      </c>
-      <c r="D15" t="s">
-        <v>186</v>
       </c>
       <c r="E15" s="1" t="b">
         <v>0</v>
@@ -6275,22 +6452,22 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>186</v>
+      </c>
+      <c r="B16" t="s">
         <v>187</v>
       </c>
-      <c r="B16" t="s">
+      <c r="C16" t="s">
+        <v>176</v>
+      </c>
+      <c r="D16" t="s">
         <v>188</v>
       </c>
-      <c r="C16" t="s">
-        <v>177</v>
-      </c>
-      <c r="D16" t="s">
-        <v>189</v>
-      </c>
       <c r="E16" s="1" t="b">
         <v>1</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H16" t="str">
         <f t="shared" si="0"/>
@@ -6302,13 +6479,13 @@
         <v>101</v>
       </c>
       <c r="B17" t="s">
+        <v>189</v>
+      </c>
+      <c r="C17" t="s">
+        <v>176</v>
+      </c>
+      <c r="D17" t="s">
         <v>190</v>
-      </c>
-      <c r="C17" t="s">
-        <v>177</v>
-      </c>
-      <c r="D17" t="s">
-        <v>191</v>
       </c>
       <c r="E17" s="1" t="b">
         <v>0</v>
@@ -6320,22 +6497,22 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>191</v>
+      </c>
+      <c r="B18" t="s">
         <v>192</v>
       </c>
-      <c r="B18" t="s">
+      <c r="C18" t="s">
         <v>193</v>
       </c>
-      <c r="C18" t="s">
+      <c r="D18" t="s">
         <v>194</v>
       </c>
-      <c r="D18" t="s">
-        <v>195</v>
-      </c>
       <c r="E18" s="1" t="b">
         <v>1</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H18" t="str">
         <f t="shared" si="0"/>
@@ -6347,46 +6524,46 @@
         <v>61</v>
       </c>
       <c r="B19" t="s">
+        <v>195</v>
+      </c>
+      <c r="C19" t="s">
         <v>196</v>
       </c>
-      <c r="C19" t="s">
+      <c r="D19" t="s">
         <v>197</v>
       </c>
-      <c r="D19" t="s">
-        <v>198</v>
-      </c>
       <c r="E19" s="1" t="b">
         <v>1</v>
       </c>
       <c r="F19" t="s">
+        <v>230</v>
+      </c>
+      <c r="H19" t="str">
+        <f t="shared" si="0"/>
+        <v>C20798</v>
+      </c>
+      <c r="I19" t="s">
         <v>231</v>
-      </c>
-      <c r="H19" t="str">
-        <f t="shared" si="0"/>
-        <v>C20798</v>
-      </c>
-      <c r="I19" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>198</v>
+      </c>
+      <c r="B20" t="s">
         <v>199</v>
       </c>
-      <c r="B20" t="s">
+      <c r="C20" t="s">
         <v>200</v>
       </c>
-      <c r="C20" t="s">
+      <c r="D20" t="s">
         <v>201</v>
       </c>
-      <c r="D20" t="s">
-        <v>202</v>
-      </c>
       <c r="E20" s="1" t="b">
         <v>1</v>
       </c>
       <c r="F20" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H20" t="str">
         <f t="shared" si="0"/>
@@ -6395,16 +6572,16 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>202</v>
+      </c>
+      <c r="B21" t="s">
         <v>203</v>
       </c>
-      <c r="B21" t="s">
+      <c r="C21" t="s">
         <v>204</v>
       </c>
-      <c r="C21" t="s">
+      <c r="D21" t="s">
         <v>205</v>
-      </c>
-      <c r="D21" t="s">
-        <v>206</v>
       </c>
       <c r="E21" s="1" t="b">
         <v>0</v>
@@ -6416,16 +6593,16 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>206</v>
+      </c>
+      <c r="B22" t="s">
         <v>207</v>
       </c>
-      <c r="B22" t="s">
+      <c r="C22" t="s">
         <v>208</v>
       </c>
-      <c r="C22" t="s">
+      <c r="D22" t="s">
         <v>209</v>
-      </c>
-      <c r="D22" t="s">
-        <v>210</v>
       </c>
       <c r="E22" s="1" t="b">
         <v>0</v>
@@ -6437,16 +6614,16 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
+        <v>210</v>
+      </c>
+      <c r="B23" t="s">
         <v>211</v>
       </c>
-      <c r="B23" t="s">
+      <c r="C23" t="s">
         <v>212</v>
       </c>
-      <c r="C23" t="s">
+      <c r="D23" t="s">
         <v>213</v>
-      </c>
-      <c r="D23" t="s">
-        <v>214</v>
       </c>
       <c r="E23" s="1" t="b">
         <v>0</v>
@@ -6461,13 +6638,13 @@
         <v>114</v>
       </c>
       <c r="B24" t="s">
+        <v>214</v>
+      </c>
+      <c r="C24" t="s">
         <v>215</v>
       </c>
-      <c r="C24" t="s">
+      <c r="D24" t="s">
         <v>216</v>
-      </c>
-      <c r="D24" t="s">
-        <v>217</v>
       </c>
       <c r="E24" s="1" t="b">
         <v>0</v>

--- a/PartsList.xlsx
+++ b/PartsList.xlsx
@@ -5,18 +5,19 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\matja\Documents\Projects\PCBs\Keyboard\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\matja\Documents\Projects\TheFalcon\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD9F0841-BB31-46B4-A99D-25E84776080D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74590BC6-52E8-4F0A-8A4D-D7BCFDC26C3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="24240" windowHeight="13020" activeTab="2" xr2:uid="{FE2F31EC-1493-4486-83E7-300EEFA8040E}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{FE2F31EC-1493-4486-83E7-300EEFA8040E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="JLCPCB(Detailed)" sheetId="3" r:id="rId3"/>
-    <sheet name="Left" sheetId="5" r:id="rId4"/>
+    <sheet name="Sheet3" sheetId="6" r:id="rId4"/>
+    <sheet name="Left" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="255">
   <si>
     <t>Name</t>
   </si>
@@ -780,6 +781,30 @@
   </si>
   <si>
     <t>https://www.digikey.co.za/en/products/detail/harvatek-corporation/T36K3BGR-05D000121U1930/13588739?srsltid=AfmBOorHMRRNAUi7aH5xRNijnPW6IsY_VAwZrTEPsSnwkcwYHddkkWbw</t>
+  </si>
+  <si>
+    <t>https://www.digikey.co.za/en/products/detail/3m/SJ5302/2345107</t>
+  </si>
+  <si>
+    <t>Cost per unit</t>
+  </si>
+  <si>
+    <t>Switch layer</t>
+  </si>
+  <si>
+    <t>Approx, depends on switch</t>
+  </si>
+  <si>
+    <t>Screws and mounts</t>
+  </si>
+  <si>
+    <t>Feet</t>
+  </si>
+  <si>
+    <t>Key caps</t>
+  </si>
+  <si>
+    <t>Estimated but depends</t>
   </si>
 </sst>
 </file>
@@ -5820,7 +5845,7 @@
       </c>
       <c r="K48" s="4"/>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>236</v>
       </c>
@@ -5838,7 +5863,7 @@
         <v>331.23</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>241</v>
       </c>
@@ -5856,7 +5881,7 @@
         <v>97.7</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>242</v>
       </c>
@@ -5865,7 +5890,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>142</v>
       </c>
@@ -5885,8 +5910,11 @@
         <f t="shared" si="21"/>
         <v>273.99</v>
       </c>
-    </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N52" s="5" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>240</v>
       </c>
@@ -5907,7 +5935,7 @@
         <v>157.58000000000001</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>243</v>
       </c>
@@ -5929,7 +5957,7 @@
       </c>
       <c r="L54" s="4"/>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>13</v>
       </c>
@@ -5943,7 +5971,7 @@
       <c r="J55" s="4"/>
       <c r="L55" s="4"/>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
       <c r="C56" s="3"/>
       <c r="D56" s="3"/>
       <c r="E56" s="3"/>
@@ -5955,7 +5983,7 @@
       </c>
       <c r="L56" s="4"/>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
       <c r="C57" s="3"/>
       <c r="D57" s="3"/>
       <c r="E57" s="3"/>
@@ -5964,7 +5992,7 @@
       <c r="K57" s="4"/>
       <c r="L57" s="4"/>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
       <c r="C58" s="3"/>
       <c r="D58" s="3"/>
       <c r="E58" s="3"/>
@@ -5973,7 +6001,7 @@
       <c r="K58" s="4"/>
       <c r="L58" s="4"/>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
       <c r="C59" s="3"/>
       <c r="D59" s="3"/>
       <c r="E59" s="3"/>
@@ -5982,7 +6010,7 @@
       <c r="K59" s="4"/>
       <c r="L59" s="4"/>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
       <c r="C60" s="3"/>
       <c r="D60" s="3"/>
       <c r="E60" s="3"/>
@@ -5991,7 +6019,7 @@
       <c r="K60" s="4"/>
       <c r="L60" s="4"/>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:14" x14ac:dyDescent="0.25">
       <c r="C61" s="3"/>
       <c r="D61" s="3"/>
       <c r="E61" s="3"/>
@@ -6000,7 +6028,7 @@
       <c r="K61" s="4"/>
       <c r="L61" s="4"/>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:14" x14ac:dyDescent="0.25">
       <c r="C62" s="3"/>
       <c r="D62" s="3"/>
       <c r="E62" s="3"/>
@@ -6009,7 +6037,7 @@
       <c r="K62" s="4"/>
       <c r="L62" s="4"/>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
       <c r="C63" s="3"/>
       <c r="D63" s="3"/>
       <c r="E63" s="3"/>
@@ -6018,7 +6046,7 @@
       <c r="K63" s="4"/>
       <c r="L63" s="4"/>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
       <c r="C64" s="3"/>
       <c r="D64" s="3"/>
       <c r="E64" s="3"/>
@@ -6096,6 +6124,120 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F034905-8035-4CC7-A6D2-656944C803C8}">
+  <dimension ref="A1:C19"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="17.28515625" customWidth="1"/>
+    <col min="2" max="2" width="18.85546875" customWidth="1"/>
+    <col min="3" max="3" width="19.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B1" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B2" s="4">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>249</v>
+      </c>
+      <c r="B3" s="4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="4">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="4"/>
+      <c r="C5" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>253</v>
+      </c>
+      <c r="B6" s="4"/>
+      <c r="C6" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>251</v>
+      </c>
+      <c r="B7" s="4">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>252</v>
+      </c>
+      <c r="B8" s="4">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B9" s="4"/>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B10" s="4"/>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B11" s="4"/>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B12" s="4">
+        <f>SUM(B2:B11)</f>
+        <v>1163</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B13" s="4"/>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B14" s="4"/>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B15" s="4"/>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B16" s="4"/>
+    </row>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B17" s="4"/>
+    </row>
+    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B18" s="4"/>
+    </row>
+    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B19" s="4"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04496EBE-FF58-4432-A51C-6782192DBBAD}">
   <dimension ref="A1:I24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
